--- a/Rose_fantawotblitz.xlsx
+++ b/Rose_fantawotblitz.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t>Rose lega FantaWotBlitz</t>
   </si>
@@ -20,7 +20,7 @@
     <t>https://leghe.fantacalcio.it/fantawotblitz</t>
   </si>
   <si>
-    <t>* Calciatori non più in campionato - Data download 30/11/2025</t>
+    <t>* Calciatori non più in campionato - Data download 18/05/2026</t>
   </si>
   <si>
     <t>ReAlcolizzati</t>
@@ -44,850 +44,847 @@
     <t>P</t>
   </si>
   <si>
+    <t>Audero</t>
+  </si>
+  <si>
+    <t>Cre</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Leali</t>
+  </si>
+  <si>
+    <t>Gen</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Provedel</t>
   </si>
   <si>
     <t>Laz</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Leali</t>
-  </si>
-  <si>
-    <t>Gen</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Mandas</t>
-  </si>
-  <si>
-    <t>Pinsoglio</t>
+    <t>Meret</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Motta</t>
+  </si>
+  <si>
+    <t>Svilar</t>
+  </si>
+  <si>
+    <t>Rom</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Dimarco</t>
+  </si>
+  <si>
+    <t>Int</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Spinazzola</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Gosens</t>
+  </si>
+  <si>
+    <t>Fio</t>
+  </si>
+  <si>
+    <t>Bastoni</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Zortea</t>
+  </si>
+  <si>
+    <t>Bol</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Di Lorenzo</t>
+  </si>
+  <si>
+    <t>Celik</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Lazaro</t>
+  </si>
+  <si>
+    <t>Tor</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Angelino</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Rrahmani</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Norton-Cuffy</t>
+  </si>
+  <si>
+    <t>Maripan</t>
+  </si>
+  <si>
+    <t>Ramon</t>
+  </si>
+  <si>
+    <t>Com</t>
+  </si>
+  <si>
+    <t>Carlos Augusto</t>
+  </si>
+  <si>
+    <t>Zè Pedro</t>
+  </si>
+  <si>
+    <t>Cag</t>
+  </si>
+  <si>
+    <t>Cabal</t>
   </si>
   <si>
     <t>Juv</t>
   </si>
   <si>
-    <t>Israel</t>
-  </si>
-  <si>
-    <t>Tor</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Svilar</t>
-  </si>
-  <si>
-    <t>Rom</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Dimarco</t>
-  </si>
-  <si>
-    <t>Int</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Cuadrado</t>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Zielinski</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Cristante</t>
+  </si>
+  <si>
+    <t>Politano</t>
+  </si>
+  <si>
+    <t>Mandragora</t>
+  </si>
+  <si>
+    <t>Calhanoglu</t>
+  </si>
+  <si>
+    <t>Pasalic</t>
+  </si>
+  <si>
+    <t>Ata</t>
+  </si>
+  <si>
+    <t>Zaniolo</t>
+  </si>
+  <si>
+    <t>Udi</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Zambo Anguissa</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>McKennie</t>
+  </si>
+  <si>
+    <t>Thuram K.</t>
+  </si>
+  <si>
+    <t>Zalewski</t>
+  </si>
+  <si>
+    <t>El Aynaoui</t>
+  </si>
+  <si>
+    <t>Isaksen</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Neres</t>
+  </si>
+  <si>
+    <t>Sucic P.</t>
+  </si>
+  <si>
+    <t>Taylor K.</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Simeone</t>
+  </si>
+  <si>
+    <t>Kean</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>Cambiaghi</t>
+  </si>
+  <si>
+    <t>Raspadori</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Thuram</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Laurientè</t>
+  </si>
+  <si>
+    <t>Sas</t>
+  </si>
+  <si>
+    <t>Hojlund</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Krstovic</t>
+  </si>
+  <si>
+    <t>Esposito F.P.</t>
+  </si>
+  <si>
+    <t>Douvikas</t>
+  </si>
+  <si>
+    <t>Durosinmi</t>
   </si>
   <si>
     <t>Pis</t>
   </si>
   <si>
-    <t>Acerbi</t>
-  </si>
-  <si>
-    <t>Bastoni</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Gosens</t>
-  </si>
-  <si>
-    <t>Fio</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>Giovane</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Crediti Residui: 0</t>
+  </si>
+  <si>
+    <t>Crediti Residui: 2</t>
+  </si>
+  <si>
+    <t>CSKA LA RISSA</t>
+  </si>
+  <si>
+    <t>Black Gay United</t>
+  </si>
+  <si>
+    <t>Skorupski</t>
+  </si>
+  <si>
+    <t>Muric</t>
+  </si>
+  <si>
+    <t>Milinkovic-Savic V.</t>
+  </si>
+  <si>
+    <t>Carnesecchi</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>De Gea</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Montipò</t>
+  </si>
+  <si>
+    <t>Ver</t>
+  </si>
+  <si>
+    <t>Mancini</t>
+  </si>
+  <si>
+    <t>Romagnoli</t>
   </si>
   <si>
     <t>Buongiorno</t>
   </si>
   <si>
-    <t>Nap</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Marusic</t>
-  </si>
-  <si>
-    <t>Di Lorenzo</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Zortea</t>
-  </si>
-  <si>
-    <t>Bol</t>
-  </si>
-  <si>
-    <t>Lazaro</t>
-  </si>
-  <si>
-    <t>Angelino</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Rrahmani</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>Bellanova</t>
+  </si>
+  <si>
+    <t>N'Dicka</t>
+  </si>
+  <si>
+    <t>Dumfries</t>
+  </si>
+  <si>
+    <t>Valeri</t>
+  </si>
+  <si>
+    <t>Par</t>
+  </si>
+  <si>
+    <t>De Winter</t>
+  </si>
+  <si>
+    <t>Mil</t>
+  </si>
+  <si>
+    <t>Dodò</t>
+  </si>
+  <si>
+    <t>Ostigard</t>
+  </si>
+  <si>
+    <t>Solet</t>
+  </si>
+  <si>
+    <t>Baschirotto</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Wesley</t>
+  </si>
+  <si>
+    <t>Kelly L.</t>
+  </si>
+  <si>
+    <t>Belghali</t>
+  </si>
+  <si>
+    <t>Kempf</t>
+  </si>
+  <si>
+    <t>De Roon</t>
+  </si>
+  <si>
+    <t>Rabiot</t>
+  </si>
+  <si>
+    <t>Zaccagni</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Odgaard</t>
+  </si>
+  <si>
+    <t>Kostic</t>
+  </si>
+  <si>
+    <t>Elmas</t>
+  </si>
+  <si>
+    <t>Saelemaekers</t>
+  </si>
+  <si>
+    <t>Da Cunha</t>
+  </si>
+  <si>
+    <t>Tramoni M.</t>
+  </si>
+  <si>
+    <t>Vlasic</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Konè M.</t>
+  </si>
+  <si>
+    <t>Ederson D.S.</t>
+  </si>
+  <si>
+    <t>Bernabè</t>
+  </si>
+  <si>
+    <t>Casadei</t>
+  </si>
+  <si>
+    <t>Paz N.</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Atta</t>
+  </si>
+  <si>
+    <t>Berardi</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Pinamonti</t>
+  </si>
+  <si>
+    <t>Fullkrug</t>
+  </si>
+  <si>
+    <t>Boga</t>
+  </si>
+  <si>
+    <t>Esposito Se.</t>
+  </si>
+  <si>
+    <t>Moreo</t>
+  </si>
+  <si>
+    <t>Castro S.</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Malen</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Bonny</t>
+  </si>
+  <si>
+    <t>Yildiz</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Vaz</t>
+  </si>
+  <si>
+    <t>Adams C.</t>
+  </si>
+  <si>
+    <t>Crediti Residui: 11</t>
+  </si>
+  <si>
+    <t>Chianti e Pianti</t>
+  </si>
+  <si>
+    <t>FC Tumori</t>
+  </si>
+  <si>
+    <t>Caprile</t>
+  </si>
+  <si>
+    <t>Terracciano</t>
+  </si>
+  <si>
+    <t>Butez</t>
+  </si>
+  <si>
+    <t>Maignan</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Tornqvist</t>
+  </si>
+  <si>
+    <t>Torriani</t>
+  </si>
+  <si>
+    <t>Darmian</t>
+  </si>
+  <si>
+    <t>Akanji</t>
+  </si>
+  <si>
+    <t>Kalulu</t>
+  </si>
+  <si>
+    <t>Gabbia</t>
+  </si>
+  <si>
+    <t>Cambiaso</t>
+  </si>
+  <si>
+    <t>Tomori</t>
+  </si>
+  <si>
+    <t>Zanoli</t>
+  </si>
+  <si>
+    <t>Vojvoda</t>
+  </si>
+  <si>
+    <t>Doig</t>
+  </si>
+  <si>
+    <t>Pavlovic</t>
+  </si>
+  <si>
+    <t>Bartesaghi</t>
+  </si>
+  <si>
+    <t>Scalvini</t>
+  </si>
+  <si>
+    <t>Valle</t>
+  </si>
+  <si>
+    <t>Gatti</t>
+  </si>
+  <si>
+    <t>Joao Mario</t>
+  </si>
+  <si>
+    <t>Bella-Kotchap</t>
+  </si>
+  <si>
+    <t>Pellegrini Lo.</t>
+  </si>
+  <si>
+    <t>Pulisic</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Orsolini</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Loftus-Cheek</t>
+  </si>
+  <si>
+    <t>Lobotka</t>
+  </si>
+  <si>
+    <t>Thorsby</t>
+  </si>
+  <si>
+    <t>Coulibaly L.</t>
+  </si>
+  <si>
+    <t>Lec</t>
+  </si>
+  <si>
+    <t>Maldini</t>
+  </si>
+  <si>
+    <t>Miretti</t>
+  </si>
+  <si>
+    <t>Gilmour</t>
+  </si>
+  <si>
+    <t>Iling Junior</t>
+  </si>
+  <si>
+    <t>Gudmundsson A.</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Conceicao</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>Baturina</t>
+  </si>
+  <si>
+    <t>Rowe</t>
+  </si>
+  <si>
+    <t>Bonazzoli</t>
+  </si>
+  <si>
+    <t>Vlahovic</t>
+  </si>
+  <si>
+    <t>Lukaku</t>
+  </si>
+  <si>
+    <t>Leao</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Nkunku</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Sarr A.</t>
+  </si>
+  <si>
+    <t>Cancellieri</t>
+  </si>
+  <si>
+    <t>Cheddira</t>
+  </si>
+  <si>
+    <t>Davis K.</t>
+  </si>
+  <si>
+    <t>Rodriguez Je.</t>
+  </si>
+  <si>
+    <t>Bowie</t>
+  </si>
+  <si>
+    <t>Crediti Residui: 37</t>
+  </si>
+  <si>
+    <t>Crediti Residui: 24</t>
+  </si>
+  <si>
+    <t>Canile Comunale Di Merate</t>
+  </si>
+  <si>
+    <t>FC ETTANERA</t>
+  </si>
+  <si>
+    <t>Perin</t>
+  </si>
+  <si>
+    <t>Di Gennaro</t>
+  </si>
+  <si>
+    <t>Falcone</t>
+  </si>
+  <si>
+    <t>Sommer</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Di Gregorio</t>
+  </si>
+  <si>
+    <t>Martinez Jo.</t>
+  </si>
+  <si>
+    <t>Juan Jesus</t>
+  </si>
+  <si>
+    <t>Luperto</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Mina</t>
+  </si>
+  <si>
+    <t>Bremer</t>
+  </si>
+  <si>
+    <t>Gutierrez</t>
+  </si>
+  <si>
+    <t>Vasquez</t>
   </si>
   <si>
     <t>Holm</t>
   </si>
   <si>
-    <t>Carlos Augusto</t>
-  </si>
-  <si>
-    <t>Olivera</t>
+    <t>Obert</t>
+  </si>
+  <si>
+    <t>Hien</t>
+  </si>
+  <si>
+    <t>Gila</t>
+  </si>
+  <si>
+    <t>Bisseck</t>
+  </si>
+  <si>
+    <t>Circati</t>
   </si>
   <si>
     <t>Comuzzo</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Politano</t>
-  </si>
-  <si>
-    <t>El Shaarawy</t>
-  </si>
-  <si>
-    <t>Calhanoglu</t>
-  </si>
-  <si>
-    <t>Mandragora</t>
-  </si>
-  <si>
-    <t>Mkhitaryan</t>
-  </si>
-  <si>
-    <t>Guendouzi</t>
-  </si>
-  <si>
-    <t>Zaniolo</t>
-  </si>
-  <si>
-    <t>Udi</t>
-  </si>
-  <si>
-    <t>Zambo Anguissa</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>McKennie</t>
-  </si>
-  <si>
-    <t>Thuram K.</t>
-  </si>
-  <si>
-    <t>Zalewski</t>
-  </si>
-  <si>
-    <t>Ata</t>
-  </si>
-  <si>
-    <t>Koopmeiners</t>
-  </si>
-  <si>
-    <t>Isaksen</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Prati</t>
-  </si>
-  <si>
-    <t>Cag</t>
-  </si>
-  <si>
-    <t>Sucic P.</t>
-  </si>
-  <si>
-    <t>Stanciu</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Simeone</t>
+    <t>Palestra</t>
+  </si>
+  <si>
+    <t>Delprato</t>
+  </si>
+  <si>
+    <t>Barella</t>
+  </si>
+  <si>
+    <t>Cataldi</t>
+  </si>
+  <si>
+    <t>Mazzitelli</t>
+  </si>
+  <si>
+    <t>Locatelli</t>
+  </si>
+  <si>
+    <t>De Bruyne</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Modric</t>
+  </si>
+  <si>
+    <t>Gaetano</t>
+  </si>
+  <si>
+    <t>McTominay</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Malinovskyi</t>
+  </si>
+  <si>
+    <t>Caqueret</t>
+  </si>
+  <si>
+    <t>Thorstvedt</t>
+  </si>
+  <si>
+    <t>Ekkelenkamp</t>
+  </si>
+  <si>
+    <t>Perrone</t>
+  </si>
+  <si>
+    <t>Vandeputte</t>
+  </si>
+  <si>
+    <t>Konè I.</t>
+  </si>
+  <si>
+    <t>Vergara</t>
+  </si>
+  <si>
+    <t>Scamacca</t>
   </si>
   <si>
     <t>Dybala</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Cambiaghi</t>
-  </si>
-  <si>
-    <t>Kean</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>Thuram</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>Pedro</t>
-  </si>
-  <si>
-    <t>Hojlund</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>Laurientè</t>
-  </si>
-  <si>
-    <t>Sas</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Diao</t>
-  </si>
-  <si>
-    <t>Com</t>
-  </si>
-  <si>
-    <t>Krstovic</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Esposito F.P.</t>
-  </si>
-  <si>
-    <t>Douvikas</t>
-  </si>
-  <si>
-    <t>Crediti Residui: 1</t>
-  </si>
-  <si>
-    <t>Crediti Residui: 9</t>
-  </si>
-  <si>
-    <t>CSKA LA RISSA</t>
-  </si>
-  <si>
-    <t>Black Gay United</t>
-  </si>
-  <si>
-    <t>Milinkovic-Savic V.</t>
-  </si>
-  <si>
-    <t>Audero</t>
-  </si>
-  <si>
-    <t>Cre</t>
-  </si>
-  <si>
-    <t>De Gea</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Carnesecchi</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Martinelli T.</t>
-  </si>
-  <si>
-    <t>Okoye</t>
-  </si>
-  <si>
-    <t>Pezzella Giu.</t>
-  </si>
-  <si>
-    <t>Romagnoli</t>
-  </si>
-  <si>
-    <t>Mancini</t>
-  </si>
-  <si>
-    <t>Bellanova</t>
-  </si>
-  <si>
-    <t>Ranieri L.</t>
-  </si>
-  <si>
-    <t>Dumfries</t>
-  </si>
-  <si>
-    <t>Kamara H.</t>
-  </si>
-  <si>
-    <t>De Winter</t>
-  </si>
-  <si>
-    <t>Mil</t>
-  </si>
-  <si>
-    <t>Valeri</t>
-  </si>
-  <si>
-    <t>Par</t>
-  </si>
-  <si>
-    <t>Ostigard</t>
-  </si>
-  <si>
-    <t>Dodò</t>
-  </si>
-  <si>
-    <t>Baschirotto</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Solet</t>
-  </si>
-  <si>
-    <t>Veiga D.</t>
-  </si>
-  <si>
-    <t>Lec</t>
-  </si>
-  <si>
-    <t>Wesley</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Vitik</t>
-  </si>
-  <si>
-    <t>De Roon</t>
-  </si>
-  <si>
-    <t>Rabiot</t>
-  </si>
-  <si>
-    <t>Zaccagni</t>
-  </si>
-  <si>
-    <t>Odgaard</t>
-  </si>
-  <si>
-    <t>Frattesi</t>
-  </si>
-  <si>
-    <t>Elmas</t>
-  </si>
-  <si>
-    <t>Saelemaekers</t>
-  </si>
-  <si>
-    <t>Da Cunha</t>
-  </si>
-  <si>
-    <t>Tramoni M.</t>
-  </si>
-  <si>
-    <t>Vlasic</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Konè M.</t>
-  </si>
-  <si>
-    <t>Ederson D.S.</t>
-  </si>
-  <si>
-    <t>Bernabè</t>
-  </si>
-  <si>
-    <t>Casadei</t>
-  </si>
-  <si>
-    <t>Paz N.</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>Atta</t>
-  </si>
-  <si>
-    <t>Berardi</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Morata</t>
-  </si>
-  <si>
-    <t>Dzeko</t>
+    <t>Martinez L.</t>
+  </si>
+  <si>
+    <t>85</t>
   </si>
   <si>
     <t>Zapata D.</t>
   </si>
   <si>
-    <t>Cutrone</t>
-  </si>
-  <si>
-    <t>Pinamonti</t>
-  </si>
-  <si>
-    <t>Esposito Se.</t>
-  </si>
-  <si>
-    <t>Lookman</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Castro S.</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>Yildiz</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>Bonny</t>
-  </si>
-  <si>
-    <t>Adams C.</t>
-  </si>
-  <si>
-    <t>Crediti Residui: 0</t>
-  </si>
-  <si>
-    <t>Crediti Residui: 13</t>
-  </si>
-  <si>
-    <t>Chianti e Pianti</t>
-  </si>
-  <si>
-    <t>FC Tumori</t>
-  </si>
-  <si>
-    <t>Caprile</t>
-  </si>
-  <si>
-    <t>Terracciano</t>
-  </si>
-  <si>
-    <t>Suzuki</t>
-  </si>
-  <si>
-    <t>Maignan</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Butez</t>
-  </si>
-  <si>
-    <t>Torriani</t>
-  </si>
-  <si>
-    <t>Kalulu</t>
-  </si>
-  <si>
-    <t>Akanji</t>
-  </si>
-  <si>
-    <t>Cambiaso</t>
-  </si>
-  <si>
-    <t>Gabbia</t>
-  </si>
-  <si>
-    <t>Zanoli</t>
-  </si>
-  <si>
-    <t>Tomori</t>
-  </si>
-  <si>
-    <t>Doig</t>
-  </si>
-  <si>
-    <t>Pavlovic</t>
-  </si>
-  <si>
-    <t>Valle</t>
-  </si>
-  <si>
-    <t>Scalvini</t>
-  </si>
-  <si>
-    <t>Rui Modesto</t>
-  </si>
-  <si>
-    <t>Tavares N.</t>
+    <t>Colombo</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Vardy</t>
+  </si>
+  <si>
+    <t>Vitinha O.</t>
+  </si>
+  <si>
+    <t>Soulè</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Orban G.</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>De Ketelaere</t>
+  </si>
+  <si>
+    <t>Kilicsoy</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>Joao Mario</t>
-  </si>
-  <si>
-    <t>Gatti</t>
-  </si>
-  <si>
-    <t>Kouadio</t>
-  </si>
-  <si>
-    <t>Bella-Kotchap</t>
-  </si>
-  <si>
-    <t>Ver</t>
-  </si>
-  <si>
-    <t>Orsolini</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>Freuler</t>
-  </si>
-  <si>
-    <t>Sergi Roberto</t>
-  </si>
-  <si>
-    <t>Pulisic</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Lobotka</t>
-  </si>
-  <si>
-    <t>Loftus-Cheek</t>
-  </si>
-  <si>
-    <t>Zhegrova</t>
-  </si>
-  <si>
-    <t>Maldini</t>
-  </si>
-  <si>
-    <t>Carboni V.</t>
-  </si>
-  <si>
-    <t>Gudmundsson A.</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Folorunsho</t>
-  </si>
-  <si>
-    <t>Bondo</t>
-  </si>
-  <si>
-    <t>Conceicao</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Rowe</t>
-  </si>
-  <si>
-    <t>Baturina</t>
-  </si>
-  <si>
-    <t>Jashari</t>
-  </si>
-  <si>
-    <t>Sanabria</t>
-  </si>
-  <si>
-    <t>Vlahovic</t>
-  </si>
-  <si>
-    <t>Lukaku</t>
-  </si>
-  <si>
-    <t>Leao</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>Piccoli</t>
-  </si>
-  <si>
-    <t>Nkunku</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>Davis K.</t>
-  </si>
-  <si>
-    <t>Lucca</t>
-  </si>
-  <si>
-    <t>Dia</t>
-  </si>
-  <si>
-    <t>Openda</t>
-  </si>
-  <si>
-    <t>Camarda</t>
-  </si>
-  <si>
-    <t>Crediti Residui: 20</t>
-  </si>
-  <si>
-    <t>Canile Comunale Di Merate</t>
-  </si>
-  <si>
-    <t>FC ETTANERA</t>
-  </si>
-  <si>
-    <t>Skorupski</t>
-  </si>
-  <si>
-    <t>Di Gennaro</t>
-  </si>
-  <si>
-    <t>Meret</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Sommer</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Di Gregorio</t>
-  </si>
-  <si>
-    <t>Martinez Jo.</t>
-  </si>
-  <si>
-    <t>Zappacosta</t>
-  </si>
-  <si>
-    <t>Biraghi</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
-    <t>Luperto</t>
-  </si>
-  <si>
-    <t>Bremer</t>
-  </si>
-  <si>
-    <t>Mina</t>
-  </si>
-  <si>
-    <t>Miranda J.</t>
-  </si>
-  <si>
-    <t>Estupinan</t>
-  </si>
-  <si>
-    <t>Kossounou</t>
-  </si>
-  <si>
-    <t>Hien</t>
-  </si>
-  <si>
-    <t>Viti</t>
-  </si>
-  <si>
-    <t>Bisseck</t>
-  </si>
-  <si>
-    <t>Beukema</t>
-  </si>
-  <si>
-    <t>Delprato</t>
-  </si>
-  <si>
-    <t>Kouassi</t>
-  </si>
-  <si>
-    <t>Floriani Mussolini</t>
-  </si>
-  <si>
-    <t>Barella</t>
-  </si>
-  <si>
-    <t>Locatelli</t>
-  </si>
-  <si>
-    <t>Pasalic</t>
-  </si>
-  <si>
-    <t>Modric</t>
-  </si>
-  <si>
-    <t>De Bruyne</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Rovella</t>
-  </si>
-  <si>
-    <t>Bailey</t>
-  </si>
-  <si>
-    <t>McTominay</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Fofana Y.</t>
-  </si>
-  <si>
-    <t>Samardzic</t>
-  </si>
-  <si>
-    <t>Thorstvedt</t>
-  </si>
-  <si>
-    <t>Zerbin</t>
-  </si>
-  <si>
-    <t>Oristanio</t>
-  </si>
-  <si>
-    <t>Suslov</t>
-  </si>
-  <si>
-    <t>Neres</t>
-  </si>
-  <si>
-    <t>Dele-Bashiru</t>
-  </si>
-  <si>
-    <t>Scamacca</t>
-  </si>
-  <si>
-    <t>Immobile</t>
-  </si>
-  <si>
-    <t>Martinez L.</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>Vardy</t>
-  </si>
-  <si>
-    <t>Castellanos</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>Soulè</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Dovbyk</t>
-  </si>
-  <si>
-    <t>De Ketelaere</t>
-  </si>
-  <si>
-    <t>Gimenez</t>
-  </si>
-  <si>
-    <t>Ferguson E.</t>
-  </si>
-  <si>
-    <t>Lang</t>
-  </si>
-  <si>
     <t>Pellegrino M.</t>
-  </si>
-  <si>
-    <t>Crediti Residui: 7</t>
-  </si>
-  <si>
-    <t>Crediti Residui: 11</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1121,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>12</v>
@@ -1133,13 +1130,13 @@
         <v>9</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1147,13 +1144,13 @@
         <v>9</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>9</v>
@@ -1188,10 +1185,10 @@
         <v>29</v>
       </c>
       <c r="H10" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -1202,22 +1199,22 @@
         <v>31</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="0" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -1225,25 +1222,25 @@
         <v>25</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -1251,13 +1248,13 @@
         <v>25</v>
       </c>
       <c r="B13" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>25</v>
@@ -1266,10 +1263,10 @@
         <v>41</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -1277,25 +1274,25 @@
         <v>25</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -1303,25 +1300,25 @@
         <v>25</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1329,22 @@
         <v>50</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -1355,10 +1352,10 @@
         <v>25</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>12</v>
@@ -1367,88 +1364,88 @@
         <v>25</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H18" s="0" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>12</v>
@@ -1456,114 +1453,114 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>27</v>
@@ -1572,13 +1569,13 @@
         <v>12</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>12</v>
@@ -1586,169 +1583,169 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>96</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="11"/>
       <c r="F32" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
@@ -1756,13 +1753,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="7"/>
       <c r="F34" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -1799,22 +1796,22 @@
         <v>9</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F36" s="0" t="s">
         <v>9</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>12</v>
@@ -1825,13 +1822,13 @@
         <v>9</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>9</v>
@@ -1840,7 +1837,7 @@
         <v>107</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>108</v>
@@ -1854,19 +1851,19 @@
         <v>109</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>9</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>12</v>
@@ -1877,25 +1874,25 @@
         <v>25</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
@@ -1903,25 +1900,25 @@
         <v>25</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F40" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -1929,19 +1926,19 @@
         <v>25</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H41" s="0" t="s">
         <v>27</v>
@@ -1955,25 +1952,25 @@
         <v>25</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="F42" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43">
@@ -1981,25 +1978,25 @@
         <v>25</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H43" s="0" t="s">
         <v>14</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44">
@@ -2007,25 +2004,25 @@
         <v>25</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="F44" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45">
@@ -2033,25 +2030,25 @@
         <v>25</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="F45" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -2059,13 +2056,13 @@
         <v>25</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="F46" s="0" t="s">
         <v>25</v>
@@ -2074,33 +2071,33 @@
         <v>131</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>132</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>133</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>108</v>
@@ -2108,25 +2105,25 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>134</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>24</v>
@@ -2134,319 +2131,319 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C52" s="0" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C55" s="0" t="s">
         <v>90</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>142</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -2506,7 +2503,7 @@
         <v>170</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>12</v>
@@ -2518,7 +2515,7 @@
         <v>171</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>12</v>
@@ -2532,10 +2529,10 @@
         <v>172</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F66" s="0" t="s">
         <v>9</v>
@@ -2544,7 +2541,7 @@
         <v>173</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>174</v>
@@ -2558,10 +2555,10 @@
         <v>175</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>9</v>
@@ -2570,7 +2567,7 @@
         <v>176</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>12</v>
@@ -2584,10 +2581,10 @@
         <v>177</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="F68" s="0" t="s">
         <v>25</v>
@@ -2599,7 +2596,7 @@
         <v>27</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69">
@@ -2610,10 +2607,10 @@
         <v>179</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="F69" s="0" t="s">
         <v>25</v>
@@ -2622,10 +2619,10 @@
         <v>180</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70">
@@ -2636,10 +2633,10 @@
         <v>181</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="F70" s="0" t="s">
         <v>25</v>
@@ -2648,10 +2645,10 @@
         <v>182</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71">
@@ -2662,10 +2659,10 @@
         <v>183</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>25</v>
@@ -2674,10 +2671,10 @@
         <v>184</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
@@ -2688,10 +2685,10 @@
         <v>185</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="F72" s="0" t="s">
         <v>25</v>
@@ -2700,10 +2697,10 @@
         <v>186</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
@@ -2714,10 +2711,10 @@
         <v>187</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>25</v>
@@ -2726,10 +2723,10 @@
         <v>188</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>189</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
@@ -2737,25 +2734,25 @@
         <v>25</v>
       </c>
       <c r="B74" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="C74" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F74" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G74" s="0" t="s">
-        <v>191</v>
-      </c>
       <c r="H74" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75">
@@ -2763,22 +2760,22 @@
         <v>25</v>
       </c>
       <c r="B75" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G75" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="C75" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G75" s="0" t="s">
-        <v>193</v>
-      </c>
       <c r="H75" s="0" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>12</v>
@@ -2786,285 +2783,285 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B76" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="H76" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C76" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F76" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G76" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="H76" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B77" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G77" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="C77" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G77" s="0" t="s">
-        <v>199</v>
-      </c>
       <c r="H77" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B79" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G79" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="C79" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F79" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G79" s="0" t="s">
-        <v>204</v>
-      </c>
       <c r="H79" s="0" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B80" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F80" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G80" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="C80" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F80" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G80" s="0" t="s">
-        <v>206</v>
-      </c>
       <c r="H80" s="0" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>207</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B81" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="H81" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="C81" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F81" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G81" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="H81" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B82" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C82" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D82" s="1" t="s">
+      <c r="F82" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G82" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="F82" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G82" s="0" t="s">
-        <v>212</v>
-      </c>
       <c r="H82" s="0" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B83" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G83" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="C83" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F83" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G83" s="0" t="s">
-        <v>214</v>
-      </c>
       <c r="H83" s="0" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B84" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F84" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G84" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="C84" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G84" s="0" t="s">
-        <v>216</v>
-      </c>
       <c r="H84" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B85" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G85" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="C85" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F85" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G85" s="0" t="s">
+      <c r="H85" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="H85" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B86" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C86" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F86" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>221</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>222</v>
@@ -3072,91 +3069,91 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>223</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G87" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="F87" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G87" s="0" t="s">
-        <v>225</v>
-      </c>
       <c r="H87" s="0" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B88" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G88" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="C88" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F88" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G88" s="0" t="s">
-        <v>227</v>
-      </c>
       <c r="H88" s="0" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B89" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G89" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="C89" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F89" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G89" s="0" t="s">
-        <v>229</v>
-      </c>
       <c r="H89" s="0" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="11"/>
       <c r="F90" s="10" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="G90" s="10"/>
       <c r="H90" s="10"/>
@@ -3210,10 +3207,10 @@
         <v>233</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F94" s="0" t="s">
         <v>9</v>
@@ -3236,22 +3233,22 @@
         <v>235</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>38</v>
+        <v>202</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>236</v>
+        <v>68</v>
       </c>
       <c r="F95" s="0" t="s">
         <v>9</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H95" s="0" t="s">
         <v>27</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="96">
@@ -3259,10 +3256,10 @@
         <v>9</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>174</v>
@@ -3271,7 +3268,7 @@
         <v>9</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H96" s="0" t="s">
         <v>27</v>
@@ -3285,25 +3282,25 @@
         <v>25</v>
       </c>
       <c r="B97" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="C97" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G97" s="0" t="s">
-        <v>242</v>
-      </c>
       <c r="H97" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
@@ -3311,25 +3308,25 @@
         <v>25</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F98" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -3337,25 +3334,25 @@
         <v>25</v>
       </c>
       <c r="B99" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F99" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G99" s="0" t="s">
         <v>245</v>
       </c>
-      <c r="C99" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F99" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G99" s="0" t="s">
-        <v>246</v>
-      </c>
       <c r="H99" s="0" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
@@ -3363,25 +3360,25 @@
         <v>25</v>
       </c>
       <c r="B100" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G100" s="0" t="s">
-        <v>248</v>
-      </c>
       <c r="H100" s="0" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101">
@@ -3389,25 +3386,25 @@
         <v>25</v>
       </c>
       <c r="B101" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F101" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G101" s="0" t="s">
         <v>249</v>
       </c>
-      <c r="C101" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F101" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G101" s="0" t="s">
-        <v>250</v>
-      </c>
       <c r="H101" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102">
@@ -3415,19 +3412,19 @@
         <v>25</v>
       </c>
       <c r="B102" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102" s="0" t="s">
         <v>251</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G102" s="0" t="s">
-        <v>252</v>
       </c>
       <c r="H102" s="0" t="s">
         <v>27</v>
@@ -3441,25 +3438,25 @@
         <v>25</v>
       </c>
       <c r="B103" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G103" s="0" t="s">
         <v>253</v>
       </c>
-      <c r="C103" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G103" s="0" t="s">
-        <v>254</v>
-      </c>
       <c r="H103" s="0" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104">
@@ -3467,163 +3464,163 @@
         <v>25</v>
       </c>
       <c r="B104" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F104" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="0" t="s">
         <v>255</v>
       </c>
-      <c r="C104" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G104" s="0" t="s">
-        <v>256</v>
-      </c>
       <c r="H104" s="0" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B106" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G106" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="C106" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F106" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G106" s="0" t="s">
-        <v>260</v>
-      </c>
       <c r="H106" s="0" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B107" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C107" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D107" s="1" t="s">
+      <c r="F107" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G107" s="0" t="s">
         <v>262</v>
       </c>
-      <c r="F107" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G107" s="0" t="s">
-        <v>263</v>
-      </c>
       <c r="H107" s="0" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B108" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F108" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G108" s="0" t="s">
         <v>264</v>
       </c>
-      <c r="C108" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F108" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G108" s="0" t="s">
+      <c r="H108" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I108" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="H108" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B109" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F109" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G109" s="0" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="D109" s="1" t="s">
+      <c r="H109" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F109" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G109" s="0" t="s">
-        <v>268</v>
-      </c>
-      <c r="H109" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>90</v>
@@ -3632,13 +3629,13 @@
         <v>12</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>12</v>
@@ -3646,25 +3643,25 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B111" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F111" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G111" s="0" t="s">
         <v>271</v>
       </c>
-      <c r="C111" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F111" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G111" s="0" t="s">
-        <v>272</v>
-      </c>
       <c r="H111" s="0" t="s">
-        <v>194</v>
+        <v>11</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>12</v>
@@ -3672,181 +3669,181 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B112" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="C112" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F112" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G112" s="0" t="s">
         <v>273</v>
       </c>
-      <c r="C112" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F112" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G112" s="0" t="s">
-        <v>274</v>
-      </c>
       <c r="H112" s="0" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B113" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F113" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G113" s="0" t="s">
         <v>275</v>
       </c>
-      <c r="C113" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F113" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G113" s="0" t="s">
-        <v>276</v>
-      </c>
       <c r="H113" s="0" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>39</v>
+        <v>210</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F114" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G114" s="0" t="s">
         <v>278</v>
       </c>
-      <c r="F114" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G114" s="0" t="s">
-        <v>279</v>
-      </c>
       <c r="H114" s="0" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B115" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C115" s="0" t="s">
+      <c r="F115" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G115" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="H115" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="F115" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G115" s="0" t="s">
-        <v>282</v>
-      </c>
-      <c r="H115" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="I115" s="1" t="s">
-        <v>283</v>
+        <v>143</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B116" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="G116" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="H116" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C116" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F116" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G116" s="0" t="s">
-        <v>285</v>
-      </c>
-      <c r="H116" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B117" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="C117" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C117" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F117" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>287</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B118" s="0" t="s">
         <v>288</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>12</v>
+        <v>289</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>15</v>
@@ -3854,13 +3851,13 @@
     </row>
     <row r="119">
       <c r="A119" s="10" t="s">
-        <v>290</v>
+        <v>101</v>
       </c>
       <c r="B119" s="10"/>
       <c r="C119" s="10"/>
       <c r="D119" s="11"/>
       <c r="F119" s="10" t="s">
-        <v>291</v>
+        <v>100</v>
       </c>
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
